--- a/results/andar_할인율모니터링_20260818.xlsx
+++ b/results/andar_할인율모니터링_20260818.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,7 +491,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7,308</t>
+          <t>7,313</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -545,163 +545,163 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>EPTBG-01</t>
+          <t>EPTSC-04</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>에어플라이 프리런 러닝 벨트</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>27,000</t>
+          <t>29,900</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EOTBG-13</t>
+          <t>EPTSC-05</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>멀티 포켓 숄더 앤 크로스백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>63,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>54,000</t>
+          <t>29,900</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>398</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ENTBG-05</t>
+          <t>EPTSC-06</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>미니 숄더 앤 크로스백</t>
+          <t>[3 SET] 필라테스 삭스</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>41,700</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>29,900</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>4,950</t>
+          <t>300</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14076&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>EOTBG-19</t>
+          <t>EOTBG-13</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>위켄드 호보백</t>
+          <t>멀티 포켓 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>63,000</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>54,000</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>398</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -713,126 +713,126 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10478&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>EPTSC-04</t>
+          <t>ENTBG-05</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>미니 숄더 앤 크로스백</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>4,952</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15369&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>EPTSC-05</t>
+          <t>EOTBG-19</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>위켄드 호보백</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>47</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17443&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17414&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EPTSC-06</t>
+          <t>EPTBG-01</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>[3 SET] 필라테스 삭스</t>
+          <t>에어플라이 프리런 러닝 벨트</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>41,700</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>29,900</t>
+          <t>27,000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -1037,7 +1037,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1049,121 +1049,121 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EPTBG-03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>맨즈 라이트 러닝 베스트</t>
+          <t>컴팩트 포켓 크로스백</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>90</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16868&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>EPTBG-03</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>컴팩트 포켓 크로스백</t>
+          <t>맨즈 라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>10</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ENTBG-16</t>
+          <t>EMTBG-12</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>라이트 패딩 쇼퍼백</t>
+          <t>데일리 쇼퍼백</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>65,000</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1217,37 +1217,37 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9620&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12765&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>EMTBG-12</t>
+          <t>ENTBG-16</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>데일리 쇼퍼백</t>
+          <t>라이트 패딩 쇼퍼백</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>65,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>590</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>안다르 실버 리유저블백</t>
+          <t>안다르 실버 리유저블백 M</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1511,17 +1511,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ENTBG-18</t>
+          <t>EOTBG-20</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>시티 플로우 빅 숄더백</t>
+          <t>클라우드 스트링 쇼퍼백</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1531,17 +1531,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>67,000</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>30</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15428&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12487&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>EOTBG-20</t>
+          <t>ENTBG-18</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>클라우드 스트링 쇼퍼백</t>
+          <t>시티 플로우 빅 숄더백</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1573,17 +1573,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>67,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>444</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1595,121 +1595,121 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ENTBG-13</t>
+          <t>EOTBG-10</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>데일리 스퀘어백</t>
+          <t>에어플라이 투웨이 프리런 백 3.0</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>404</t>
+          <t>1,101</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>3.0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>EOTBG-10</t>
+          <t>EOTBO-01</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>에어플라이 투웨이 프리런 백 3.0</t>
+          <t>액티브 스포츠 보틀 (650ml)</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>1,101</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12318&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>EOTBO-01</t>
+          <t>ENTBG-13</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>액티브 스포츠 보틀 (650ml)</t>
+          <t>데일리 스퀘어백</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>49,000</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>15,000</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>404</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1931,27 +1931,27 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>EPTET-01</t>
+          <t>EPTBG-05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>언더웨어 파우치</t>
+          <t>안다르 시그니처 로고 에코백</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20,000</t>
+          <t>39,000</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1961,12 +1961,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>7</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
@@ -2015,42 +2015,42 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16629&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ENTSC-12</t>
+          <t>EPTET-01</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
+          <t>언더웨어 파우치</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>20,000</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>3,428</t>
+          <t>308</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2062,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>ENTSC-12</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2099,84 +2099,84 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15432&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EPTCP-03</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>썬가드 와이드 버킷햇</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 토삭스</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>3,428</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17437&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EJPMS-05</t>
+          <t>EPTCP-03</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>릴렉스 마사지 스틱 Ⅱ</t>
+          <t>썬가드 와이드 버킷햇</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9,500</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>4%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>10,293</t>
+          <t>36</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
@@ -2225,37 +2225,37 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=5144&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ENTSO-02</t>
+          <t>EJPMS-05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>안다르 제트플라이 (우먼즈)</t>
+          <t>릴렉스 마사지 스틱 Ⅱ</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>139,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>95,000</t>
+          <t>9,500</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>4%</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>1,014</t>
+          <t>10,293</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ENTSO-12</t>
+          <t>ENTSO-02</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2309,79 +2309,79 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14059&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>EOTMK-01</t>
+          <t>ENTSO-12</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
+          <t>안다르 제트플라이 (우먼즈)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>139,000</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>95,000</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>1,071</t>
+          <t>1,014</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>EOTBG-12</t>
+          <t>EOTET-03</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>프리런 벨크로 러닝 벨트</t>
+          <t>라이트 러닝 베스트</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>79,000</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>55,000</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>17%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2393,205 +2393,205 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14563&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>EOTSV-04</t>
+          <t>EOTMK-01</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>프리런 라이트 러닝 밴드</t>
+          <t>UV 프로텍션 골프 마스크 (벨크로)</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>22,000</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>1,071</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13852&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=14085&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EOTET-03</t>
+          <t>EOTSV-04</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>라이트 러닝 베스트</t>
+          <t>프리런 라이트 러닝 밴드</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>79,000</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>55,000</t>
+          <t>22,000</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>122</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13853&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EOTBG-12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 무릎 보호대</t>
+          <t>프리런 벨크로 러닝 벨트</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>17%</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>1,940</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8838&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EMTSC-03</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
+          <t>[1&amp;1] 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4,772</t>
+          <t>1,941</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8817&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EOTSV-03</t>
+          <t>EMTSC-03</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>서포트 허리 보호대</t>
+          <t>[1&amp;1] 논슬립 서포트 풀 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>34,000</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>26%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>4,773</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2603,79 +2603,79 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13407&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ENTFB-01</t>
+          <t>EOTSV-03</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>에어쿨링 라인 스크런치</t>
+          <t>서포트 허리 보호대</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>34,000</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>11%</t>
+          <t>26%</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>709</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11039&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EPTSV-03</t>
+          <t>ENTFB-01</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
+          <t>에어쿨링 라인 스크런치</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>203</t>
+          <t>709</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2687,121 +2687,121 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16631&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EOTCP-01</t>
+          <t>EPTSV-03</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>올라운드 버킷햇</t>
+          <t>컴프레션 카프 슬리브 (종아리 보호대)</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>69,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>59,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>203</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13215&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTCP-01</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
+          <t>올라운드 버킷햇</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>69,000</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>59,000</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>637</t>
+          <t>340</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15350&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EOTSC-06</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>서포트 쿠션 러닝 삭스</t>
+          <t>[1&amp;1] 컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>743</t>
+          <t>639</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2813,42 +2813,42 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13854&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EOTCP-03</t>
+          <t>EOTSC-06</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>쿨 라운드 볼캡</t>
+          <t>서포트 쿠션 러닝 삭스</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>743</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -2939,37 +2939,37 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13851&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EPTFB-02</t>
+          <t>EOTCP-03</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>퍼포먼스 심리스 손목밴드</t>
+          <t>쿨 라운드 볼캡</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>207</t>
+          <t>86</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -2981,42 +2981,42 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16637&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EPTET-02</t>
+          <t>EPTFB-02</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>언더웨어 세탁망</t>
+          <t>퍼포먼스 심리스 손목밴드</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3179,7 +3179,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>672</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3191,42 +3191,42 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16844&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>EMTRB-01</t>
+          <t>EPTET-02</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>서포트 힙 밴드</t>
+          <t>언더웨어 세탁망</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>1,346</t>
+          <t>258</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3238,7 +3238,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>EMTRB-02</t>
+          <t>EMTRB-01</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -3280,7 +3280,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>EMTRB-03</t>
+          <t>EMTRB-02</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -3317,84 +3317,84 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10188&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>EMTSV-06</t>
+          <t>EMTRB-03</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>에어쿨링 손목 보호대</t>
+          <t>서포트 힙 밴드</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>1,065</t>
+          <t>1,346</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8621&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ENTSC-08</t>
+          <t>EMTSV-06</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>[5 SET] 에어컴피 크루 삭스</t>
+          <t>에어쿨링 손목 보호대</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>85,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>35,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>801</t>
+          <t>1,065</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -3443,42 +3443,42 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11027&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>EPTET-03</t>
+          <t>ENTSC-08</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>안다르 3단 양우산</t>
+          <t>[5 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>85,000</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>35,000</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>59%</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>801</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3515,7 +3515,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>4,772</t>
+          <t>4,773</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3527,111 +3527,111 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17440&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EPTSC-02</t>
+          <t>EPTET-03</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>하이 쿠션 테이핑 러닝 삭스</t>
+          <t>안다르 3단 양우산</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>33</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16847&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>EKPMT-03</t>
+          <t>EPTSC-02</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>릴렉스 논슬립 요가 타월</t>
+          <t>하이 쿠션 테이핑 러닝 삭스</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>35,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>1,525</t>
+          <t>79</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6660&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EKPMT-03</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
+          <t>릴렉스 논슬립 요가 타월</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>35,900</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3641,91 +3641,91 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>1,525</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16632&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>EOTGL-01</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>짐 글러브 2.0</t>
+          <t>[1&amp;1] 하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>25,000</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>16%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>268</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13404&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>EOTMK-02</t>
+          <t>EOTGL-01</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>소프텐션 넥마스크</t>
+          <t>짐 글러브 2.0</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>25,000</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>32,000</t>
+          <t>21,000</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>16%</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>268</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3737,37 +3737,37 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16033&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EOTSC-15</t>
+          <t>EOTMK-02</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 풀 토삭스</t>
+          <t>소프텐션 넥마스크</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>32,000</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>135</t>
+          <t>157</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -3821,42 +3821,42 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15409&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EOTGL-04</t>
+          <t>EOTSC-15</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>논슬립 스킨 요기 글러브</t>
+          <t>논슬립 퍼포먼스 풀 토삭스</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>167</t>
+          <t>135</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -3905,79 +3905,79 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15377&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>EKPRB-04</t>
+          <t>EOTGL-04</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
+          <t>논슬립 스킨 요기 글러브</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>34,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>167</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6664&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EKPRB-04</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 풀 토삭스</t>
+          <t>릴렉스 3레벨 스트레칭 롱밴드</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>34,900</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>463</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3989,42 +3989,42 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ENTMK-01</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>UV 프로텍션 맨즈 골프 마스크</t>
+          <t>맨즈 논슬립 풀 토삭스</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>23,000</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>15,000</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>35%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>1,523</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -4073,42 +4073,42 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10554&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>ENTMK-01</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
+          <t>UV 프로텍션 맨즈 골프 마스크</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>23,000</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>17,800</t>
+          <t>15,000</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>35%</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>2,999</t>
+          <t>1,523</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4157,84 +4157,84 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11456&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>[3 SET] 에어컴피 크루 삭스</t>
+          <t>[1&amp;1] 논슬립 퍼포먼스 삭스</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>51,000</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,800</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>2,999</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10953&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>EKPRB-05</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>릴렉스 4레벨 힙 밴드</t>
+          <t>[3 SET] 에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>51,000</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>21,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>519</t>
+          <t>554</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -4283,143 +4283,143 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6665&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>EOTSV-01</t>
+          <t>EKPRB-05</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>하이 서포트 무릎 보호대</t>
+          <t>릴렉스 4레벨 힙 밴드</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>21,900</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>670</t>
+          <t>519</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13405&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>ENTMT-01</t>
+          <t>EOTSV-01</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>레스트 인 마블 요가매트 (4mm)</t>
+          <t>하이 서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>8%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>672</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11962&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>ENTSC-20</t>
+          <t>ENTMT-01</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>시그니처 로고 크루 삭스</t>
+          <t>레스트 인 마블 요가매트 (4mm)</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>8%</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>261</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10948&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>EMTSC-01</t>
+          <t>ENTSC-20</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>링글 크루 삭스</t>
+          <t>시그니처 로고 크루 삭스</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>1,312</t>
+          <t>542</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4451,37 +4451,37 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8578&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EMTSC-01</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
+          <t>링글 크루 삭스</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>41,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>35,600</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>15%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>1,313</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4493,37 +4493,37 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6828&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
+          <t>[1&amp;1] 릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>25,800</t>
+          <t>41,800</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>35,600</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>38%</t>
+          <t>15%</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>481</t>
+          <t>589</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -4577,37 +4577,37 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15385&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>EMTSC-05</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
+          <t>[1&amp;1] 논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>25,800</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>6,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>30%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>481</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -4619,37 +4619,37 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8728&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>EOTSC-13</t>
+          <t>EMTSC-05</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>테이핑 테크 러닝 삭스</t>
+          <t>논슬립 서포트 하프 토삭스 (SOLID)</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>6,900</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>43%</t>
+          <t>30%</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>548</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4661,121 +4661,121 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>EOTGL-02</t>
+          <t>EOTSC-09</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>히트 런 글러브</t>
+          <t>컴프레션 러닝 니삭스</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>208</t>
+          <t>332</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17446&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>EOTSC-04</t>
+          <t>EPTSV-01</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>올데이 수피마 스니커즈 삭스</t>
+          <t>[1&amp;1] 3D 쿨링 핑거홀 팔토시</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>31,800</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>4,500</t>
+          <t>24,900</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>418</t>
+          <t>174</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16031&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EOTGL-02</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>히트 런 글러브</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>208</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -4787,42 +4787,42 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13805&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>EOTSC-14</t>
+          <t>EOTSC-04</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
+          <t>올데이 수피마 스니커즈 삭스</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>23,800</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>4,500</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>418</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -4871,37 +4871,37 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>EMTSC-27</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>올라운드 오버 니삭스</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4913,126 +4913,126 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15431&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>EOTSC-10</t>
+          <t>EOTSC-14</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>시그니처 로고 맨즈 크루 삭스</t>
+          <t>[1&amp;1] 맨즈 논슬립 토삭스</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>23,800</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>204</t>
+          <t>293</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13566&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTSC-10</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>[1&amp;1] 3D 쿨링 팔토시</t>
+          <t>시그니처 로고 맨즈 크루 삭스</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>204</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11130&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>EOTSC-16</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>논슬립 스킨 하프 토삭스</t>
+          <t>[1&amp;1] 3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5081,126 +5081,126 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>EMTSC-17</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
+          <t>[3 SET] 맨즈 클래식 삭스</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>20,700</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>16,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>14%</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>220</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10657&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8836&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>EMTSC-17</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>[3 SET] 맨즈 클래식 삭스</t>
+          <t>[1&amp;1] 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>20,700</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>16,900</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>14%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>220</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>EOTSV-02</t>
+          <t>ENTSV-01</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
+          <t>3D 쿨링 팔토시</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>29,800</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>536</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5249,37 +5249,37 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13605&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>EOTSV-02</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>[1&amp;1] 올데이 기모 삭스</t>
+          <t>[1&amp;1] 하이 서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>29,800</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>19,900</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>33%</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>150</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5291,27 +5291,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11061&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15867&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>ENTSV-01</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>3D 쿨링 팔토시</t>
+          <t>[1&amp;1] 올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -5321,49 +5321,49 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>536</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13410&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15375&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>EOTSC-09</t>
+          <t>EOTSC-16</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>컴프레션 러닝 니삭스</t>
+          <t>논슬립 스킨 하프 토삭스</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5375,37 +5375,37 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>EMTSC-04</t>
+          <t>EOTSC-01</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
+          <t>프레시 필드 니삭스</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>28%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>640</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5417,42 +5417,42 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=13408&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>EOTSC-01</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>프레시 필드 니삭스</t>
+          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>27,800</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>18,900</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>32%</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>23</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5464,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EPTSC-08</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5501,126 +5501,126 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17522&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15153&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>EPTSC-08</t>
+          <t>EOTSC-13</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>[1&amp;1] 맨즈 필라테스 삭스</t>
+          <t>테이핑 테크 러닝 삭스</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>27,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>18,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>32%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>259</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16630&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8727&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>EPTSV-02</t>
+          <t>EMTSC-04</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>하이 서포트 발목 보호대</t>
+          <t>논슬립 서포트 하프 토삭스 (HOLE)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>14,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>20%</t>
+          <t>28%</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>99</t>
+          <t>640</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16630&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>EMTSV-03</t>
+          <t>EPTSV-02</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>서포트 무릎 보호대</t>
+          <t>하이 서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>14,900</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>20%</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>1,940</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -5669,42 +5669,42 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8770&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>EPTSC-01</t>
+          <t>EMTSV-03</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>쿨 메쉬 서포트 러닝 삭스</t>
+          <t>서포트 무릎 보호대</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>5,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>1,941</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
@@ -5753,121 +5753,121 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17415&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ENTSC-13</t>
+          <t>EPTSC-01</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 크루삭스</t>
+          <t>쿨 메쉬 서포트 러닝 삭스</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>5,900</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>659</t>
+          <t>107</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11458&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>ENTSC-14</t>
+          <t>ENTSC-13</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>논슬립 퍼포먼스 니삭스</t>
+          <t>논슬립 퍼포먼스 크루삭스</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>745</t>
+          <t>659</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11459&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>ENTSC-14</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
+          <t>논슬립 퍼포먼스 니삭스</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>18%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>745</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5879,59 +5879,59 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16640&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>EPTBG-05</t>
+          <t>EMTSV-02</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>안다르 시그니처 로고 에코백</t>
+          <t>서포트 발목 보호대</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>39,000</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8769&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9996&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>EMTSV-02</t>
+          <t>EMTSC-27</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>서포트 발목 보호대</t>
+          <t>올라운드 오버 니삭스</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>690</t>
+          <t>289</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -5963,17 +5963,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9612&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>[1&amp;1] 리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -5983,17 +5983,17 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>18%</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6005,121 +6005,121 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-17</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>[1&amp;1] 레그 워머</t>
+          <t>논슬립 스킨 토삭스</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>21,800</t>
+          <t>12,900</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>15,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>27%</t>
+          <t>31%</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>85</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15376&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>EOTSC-17</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>논슬립 스킨 토삭스</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15719&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>EKPET-01</t>
+          <t>EOTSC-20</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>릴렉스 소프트 웨이트바 1kg</t>
+          <t>[1&amp;1] 레그 워머</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>20,900</t>
+          <t>21,800</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>19,000</t>
+          <t>15,900</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>9%</t>
+          <t>27%</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>589</t>
+          <t>229</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
@@ -6131,69 +6131,69 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=6666&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>EOTMU-01</t>
+          <t>EKPET-01</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>스트링 패딩 넥워머</t>
+          <t>릴렉스 소프트 웨이트바 1kg</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>20,900</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>49,000</t>
+          <t>19,000</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>9%</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>589</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16045&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>EOTCP-06</t>
+          <t>EOTMU-01</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>소프트 니트 버킷햇</t>
+          <t>스트링 패딩 넥워머</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>45,000</t>
+          <t>49,000</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -6203,12 +6203,12 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>46</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
@@ -6467,27 +6467,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16036&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>ENTSC-07</t>
+          <t>EOTCP-06</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>에어컴피 크루 삭스</t>
+          <t>소프트 니트 버킷햇</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>17,000</t>
+          <t>45,000</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -6497,71 +6497,71 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>554</t>
+          <t>52</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=10939&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>EMTSV-01</t>
+          <t>ENTSC-07</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>서포트 팔꿈치 보호대</t>
+          <t>에어컴피 크루 삭스</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>13,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>9,900</t>
+          <t>17,000</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>29%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>581</t>
+          <t>554</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=8768&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>EPTSC-07</t>
+          <t>EMTSV-01</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>맨즈 필라테스 앵클 삭스</t>
+          <t>서포트 팔꿈치 보호대</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -6571,133 +6571,133 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>9,900</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>582</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>5.0</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>ENTSC-26</t>
+          <t>ENTSC-19</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>니트 기모 오버 니삭스</t>
+          <t>맨즈 논슬립 하프 토삭스</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>17,900</t>
+          <t>7,900</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>34%</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>354</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=11963&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17386&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>ENTSC-19</t>
+          <t>EPTSC-07</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>맨즈 논슬립 하프 토삭스</t>
+          <t>맨즈 필라테스 앵클 삭스</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>13,900</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>7,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>6</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>5.0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12783&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ENTSC-24</t>
+          <t>ENTSC-26</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>웜 슬릿 레그 워머</t>
+          <t>니트 기모 오버 니삭스</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>29,000</t>
+          <t>17,900</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -6707,39 +6707,39 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>354</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12480&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>EMTSC-28</t>
+          <t>ENTSC-24</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>리브드 셔링 루즈 삭스</t>
+          <t>웜 슬릿 레그 워머</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>29,000</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -6749,49 +6749,49 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>388</t>
+          <t>297</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.6</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=9599&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>EPTSC-03</t>
+          <t>EMTSC-28</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>데일리 루즈 삭스</t>
+          <t>리브드 셔링 루즈 삭스</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>11,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>8,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>25%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>388</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -6803,42 +6803,42 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=17842&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>EOTGL-03</t>
+          <t>EPTSC-03</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>소프트 니트 플립 글러브</t>
+          <t>데일리 루즈 삭스</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>11,900</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>23,900</t>
+          <t>8,900</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25%</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>21</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
@@ -6929,17 +6929,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=16034&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ENTGL-05</t>
+          <t>EOTGL-03</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>니트 글러브</t>
+          <t>소프트 니트 플립 글러브</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>364</t>
+          <t>83</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
@@ -6971,27 +6971,27 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=12792&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>EOTSC-18</t>
+          <t>ENTGL-05</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>올데이 기모 삭스</t>
+          <t>니트 글러브</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>10,900</t>
+          <t>23,900</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -7001,29 +7001,29 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>364</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.7</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15865&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>EOTSC-19</t>
+          <t>EOTSC-18</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>레그 숏 워머</t>
+          <t>올데이 기모 삭스</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7043,7 +7043,7 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>223</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
@@ -7055,27 +7055,27 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+          <t>https://andar.co.kr/product/detail.html?product_no=15733&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>EOTSC-20</t>
+          <t>EOTSC-19</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>레그 미들 워머</t>
+          <t>레그 숏 워머</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>12,900</t>
+          <t>10,900</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -7085,54 +7085,726 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>13</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.8</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=15734&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>EOTSC-20</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>레그 미들 워머</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>12,900</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>12,900</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>4.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>https://andar.co.kr/product/detail.html?product_no=11092&amp;cate_no=2100&amp;display_group=1</t>
         </is>
       </c>
-      <c r="B160" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>ENTSC-05</t>
         </is>
       </c>
-      <c r="C160" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>에어프레시 크루 삭스</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>17,000</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
+      <c r="E161" t="inlineStr">
         <is>
           <t>5,900</t>
         </is>
       </c>
-      <c r="F160" t="inlineStr">
+      <c r="F161" t="inlineStr">
         <is>
           <t>65%</t>
         </is>
       </c>
-      <c r="G160" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>575</t>
         </is>
       </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>4.8</t>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=9988&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>EMTSC-26</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>램스울 크루 삭스</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>9,900</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>282</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=6841&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>EJFMT-01</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>[SET] 홈트레이닝 에센셜 세트 (요가매트 &amp; 요가링 &amp; 마사지 스틱)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>46,800</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>26,867</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=6841&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>EJFST-02</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>[SET] 홈트레이닝 에센셜 세트 (요가매트 &amp; 요가링 &amp; 마사지 스틱)</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>46,800</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>26,867</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=6841&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>EJPMS-05</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>[SET] 홈트레이닝 에센셜 세트 (요가매트 &amp; 요가링 &amp; 마사지 스틱)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>46,800</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>35,000</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>26,867</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=5145&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>EJPFR-04</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>릴렉스 폼롤러 Ⅱ</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>19,000</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>6,350</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17584&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>EMTBG-12</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>[1&amp;1] 데일리 백 (스퀘어백/쇼퍼백/라운드백)</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>77,000</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>1,868</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17584&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>ENTBG-13</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>[1&amp;1] 데일리 백 (스퀘어백/쇼퍼백/라운드백)</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>77,000</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>1,868</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17584&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>EOTBG-21</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>[1&amp;1] 데일리 백 (스퀘어백/쇼퍼백/라운드백)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>130,000</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>77,000</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>1,868</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=17436&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>EPTSV-01</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>3D 쿨링 핑거홀 팔토시</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>15,900</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>13,900</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>13%</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16842&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>EOTSV-04</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>[3 PCS] 러닝 용품 올인원 세트 (러닝 밴드 &amp; 무릎 보호대 &amp; 삭스)</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>57,800</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>1,542</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16842&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>EOTSV-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>[3 PCS] 러닝 용품 올인원 세트 (러닝 밴드 &amp; 무릎 보호대 &amp; 삭스)</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>57,800</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>1,542</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16842&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>EOTSC-06</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>[3 PCS] 러닝 용품 올인원 세트 (러닝 밴드 &amp; 무릎 보호대 &amp; 삭스)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>57,800</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>39,000</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>1,542</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=16636&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>EPTFB-01</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>퍼포먼스 심리스 헤드밴드</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>7,900</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>5,900</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=13843&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>EOTBG-02</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>액티브 라이트 백팩</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>69,000</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>380</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>https://andar.co.kr/product/detail.html?product_no=10940&amp;cate_no=2100&amp;display_group=1</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>ENTBG-03</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>데일리 스트링 쇼퍼백</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>79,000</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>59,000</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>655</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>4.9</t>
         </is>
       </c>
     </row>
